--- a/12600512.xlsx
+++ b/12600512.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\vaults\my vault\01-academics\01-semester\02-cap776-python\04-assignments\daily-activity-tracker\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0F38389-EFA7-4773-9D39-8C26DD93EB3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9262BE2-18B6-485D-9D8C-C74CB8C2A713}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="71">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -239,6 +239,15 @@
   </si>
   <si>
     <t>I start solving problems in codewars</t>
+  </si>
+  <si>
+    <t>Very Satisfied</t>
+  </si>
+  <si>
+    <t>I did well in my DBMS CA</t>
+  </si>
+  <si>
+    <t>I registered for my first hackathon</t>
   </si>
 </sst>
 </file>
@@ -1854,92 +1863,184 @@
       </c>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A25" s="8"/>
-      <c r="B25" s="9"/>
-      <c r="C25" s="9"/>
-      <c r="D25" s="9"/>
-      <c r="E25" s="9"/>
-      <c r="F25" s="9"/>
-      <c r="G25" s="9"/>
-      <c r="H25" s="9"/>
-      <c r="I25" s="10" t="str">
+      <c r="A25" s="8">
+        <v>46270</v>
+      </c>
+      <c r="B25" s="9">
+        <v>460</v>
+      </c>
+      <c r="C25" s="9">
+        <v>0</v>
+      </c>
+      <c r="D25" s="9">
+        <v>200</v>
+      </c>
+      <c r="E25" s="9">
+        <v>150</v>
+      </c>
+      <c r="F25" s="9">
+        <v>0</v>
+      </c>
+      <c r="G25" s="9">
+        <v>0</v>
+      </c>
+      <c r="H25" s="9">
+        <v>0</v>
+      </c>
+      <c r="I25" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J25" s="10" t="str">
+        <v>810</v>
+      </c>
+      <c r="J25" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K25" s="11"/>
-      <c r="L25" s="11"/>
-      <c r="M25" s="11"/>
+        <v>630</v>
+      </c>
+      <c r="K25" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="L25" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="M25" s="11" t="s">
+        <v>51</v>
+      </c>
       <c r="N25" s="12"/>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A26" s="8"/>
-      <c r="B26" s="9"/>
-      <c r="C26" s="9"/>
-      <c r="D26" s="9"/>
-      <c r="E26" s="9"/>
-      <c r="F26" s="9"/>
-      <c r="G26" s="9"/>
-      <c r="H26" s="9"/>
-      <c r="I26" s="10" t="str">
+      <c r="A26" s="8">
+        <v>46271</v>
+      </c>
+      <c r="B26" s="9">
+        <v>460</v>
+      </c>
+      <c r="C26" s="9">
+        <v>0</v>
+      </c>
+      <c r="D26" s="9">
+        <v>240</v>
+      </c>
+      <c r="E26" s="9">
+        <v>120</v>
+      </c>
+      <c r="F26" s="9">
+        <v>0</v>
+      </c>
+      <c r="G26" s="9">
+        <v>0</v>
+      </c>
+      <c r="H26" s="9">
+        <v>0</v>
+      </c>
+      <c r="I26" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J26" s="10" t="str">
+        <v>820</v>
+      </c>
+      <c r="J26" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K26" s="11"/>
-      <c r="L26" s="11"/>
-      <c r="M26" s="11"/>
+        <v>620</v>
+      </c>
+      <c r="K26" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="L26" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="M26" s="11" t="s">
+        <v>51</v>
+      </c>
       <c r="N26" s="12"/>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A27" s="8"/>
-      <c r="B27" s="9"/>
-      <c r="C27" s="9"/>
-      <c r="D27" s="9"/>
-      <c r="E27" s="9"/>
-      <c r="F27" s="9"/>
-      <c r="G27" s="9"/>
-      <c r="H27" s="9"/>
-      <c r="I27" s="10" t="str">
+      <c r="A27" s="8">
+        <v>46272</v>
+      </c>
+      <c r="B27" s="9">
+        <v>420</v>
+      </c>
+      <c r="C27" s="9">
+        <v>0</v>
+      </c>
+      <c r="D27" s="9">
+        <v>300</v>
+      </c>
+      <c r="E27" s="9">
+        <v>200</v>
+      </c>
+      <c r="F27" s="9">
+        <v>200</v>
+      </c>
+      <c r="G27" s="9">
+        <v>4</v>
+      </c>
+      <c r="H27" s="9">
+        <v>0</v>
+      </c>
+      <c r="I27" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J27" s="10" t="str">
+        <v>1120</v>
+      </c>
+      <c r="J27" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K27" s="11"/>
-      <c r="L27" s="11"/>
-      <c r="M27" s="11"/>
-      <c r="N27" s="12"/>
+        <v>320</v>
+      </c>
+      <c r="K27" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="L27" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="M27" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="N27" s="12" t="s">
+        <v>70</v>
+      </c>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A28" s="8"/>
-      <c r="B28" s="9"/>
-      <c r="C28" s="9"/>
-      <c r="D28" s="9"/>
-      <c r="E28" s="9"/>
-      <c r="F28" s="9"/>
-      <c r="G28" s="9"/>
-      <c r="H28" s="9"/>
-      <c r="I28" s="10" t="str">
+      <c r="A28" s="8">
+        <v>46273</v>
+      </c>
+      <c r="B28" s="9">
+        <v>420</v>
+      </c>
+      <c r="C28" s="9">
+        <v>0</v>
+      </c>
+      <c r="D28" s="9">
+        <v>240</v>
+      </c>
+      <c r="E28" s="9">
+        <v>60</v>
+      </c>
+      <c r="F28" s="9">
+        <v>350</v>
+      </c>
+      <c r="G28" s="9">
+        <v>7</v>
+      </c>
+      <c r="H28" s="9">
+        <v>0</v>
+      </c>
+      <c r="I28" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J28" s="10" t="str">
+        <v>1070</v>
+      </c>
+      <c r="J28" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K28" s="11"/>
-      <c r="L28" s="11"/>
-      <c r="M28" s="11"/>
-      <c r="N28" s="12"/>
+        <v>370</v>
+      </c>
+      <c r="K28" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="L28" s="11" t="s">
+        <v>68</v>
+      </c>
+      <c r="M28" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="N28" s="12" t="s">
+        <v>69</v>
+      </c>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A29" s="8"/>

--- a/12600512.xlsx
+++ b/12600512.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\vaults\my vault\01-academics\01-semester\02-cap776-python\04-assignments\daily-activity-tracker\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9262BE2-18B6-485D-9D8C-C74CB8C2A713}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF247376-EC90-436C-AB7E-011D3E08C28D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="75">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -248,6 +248,18 @@
   </si>
   <si>
     <t>I registered for my first hackathon</t>
+  </si>
+  <si>
+    <t>Very Unsatisfied</t>
+  </si>
+  <si>
+    <t>Excellent</t>
+  </si>
+  <si>
+    <t>Enjoy at the freshers party</t>
+  </si>
+  <si>
+    <t>Excited about the hackathon but it didn't go well</t>
   </si>
 </sst>
 </file>
@@ -2043,70 +2055,136 @@
       </c>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A29" s="8"/>
-      <c r="B29" s="9"/>
-      <c r="C29" s="9"/>
-      <c r="D29" s="9"/>
-      <c r="E29" s="9"/>
-      <c r="F29" s="9"/>
-      <c r="G29" s="9"/>
-      <c r="H29" s="9"/>
-      <c r="I29" s="10" t="str">
+      <c r="A29" s="8">
+        <v>46274</v>
+      </c>
+      <c r="B29" s="9">
+        <v>460</v>
+      </c>
+      <c r="C29" s="9">
+        <v>0</v>
+      </c>
+      <c r="D29" s="9">
+        <v>240</v>
+      </c>
+      <c r="E29" s="9">
+        <v>120</v>
+      </c>
+      <c r="F29" s="9">
+        <v>350</v>
+      </c>
+      <c r="G29" s="9">
+        <v>7</v>
+      </c>
+      <c r="H29" s="9">
+        <v>0</v>
+      </c>
+      <c r="I29" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J29" s="10" t="str">
+        <v>1170</v>
+      </c>
+      <c r="J29" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K29" s="11"/>
-      <c r="L29" s="11"/>
-      <c r="M29" s="11"/>
+        <v>270</v>
+      </c>
+      <c r="K29" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="L29" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="M29" s="11" t="s">
+        <v>51</v>
+      </c>
       <c r="N29" s="12"/>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A30" s="8"/>
-      <c r="B30" s="9"/>
-      <c r="C30" s="9"/>
-      <c r="D30" s="9"/>
-      <c r="E30" s="9"/>
-      <c r="F30" s="9"/>
-      <c r="G30" s="9"/>
-      <c r="H30" s="9"/>
-      <c r="I30" s="10" t="str">
+      <c r="A30" s="8">
+        <v>46275</v>
+      </c>
+      <c r="B30" s="9">
+        <v>430</v>
+      </c>
+      <c r="C30" s="9">
+        <v>0</v>
+      </c>
+      <c r="D30" s="9">
+        <v>300</v>
+      </c>
+      <c r="E30" s="9">
+        <v>120</v>
+      </c>
+      <c r="F30" s="9">
+        <v>200</v>
+      </c>
+      <c r="G30" s="9">
+        <v>4</v>
+      </c>
+      <c r="H30" s="9">
+        <v>0</v>
+      </c>
+      <c r="I30" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J30" s="10" t="str">
+        <v>1050</v>
+      </c>
+      <c r="J30" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K30" s="11"/>
-      <c r="L30" s="11"/>
-      <c r="M30" s="11"/>
-      <c r="N30" s="12"/>
+        <v>390</v>
+      </c>
+      <c r="K30" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="L30" s="11" t="s">
+        <v>68</v>
+      </c>
+      <c r="M30" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="N30" s="12" t="s">
+        <v>73</v>
+      </c>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A31" s="8"/>
-      <c r="B31" s="9"/>
-      <c r="C31" s="9"/>
+      <c r="A31" s="8">
+        <v>46276</v>
+      </c>
+      <c r="B31" s="9">
+        <v>480</v>
+      </c>
+      <c r="C31" s="9">
+        <v>0</v>
+      </c>
       <c r="D31" s="9"/>
       <c r="E31" s="9"/>
-      <c r="F31" s="9"/>
-      <c r="G31" s="9"/>
-      <c r="H31" s="9"/>
-      <c r="I31" s="10" t="str">
+      <c r="F31" s="9">
+        <v>100</v>
+      </c>
+      <c r="G31" s="9">
+        <v>2</v>
+      </c>
+      <c r="H31" s="9">
+        <v>0</v>
+      </c>
+      <c r="I31" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J31" s="10" t="str">
+        <v>580</v>
+      </c>
+      <c r="J31" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K31" s="11"/>
-      <c r="L31" s="11"/>
-      <c r="M31" s="11"/>
-      <c r="N31" s="12"/>
+        <v>860</v>
+      </c>
+      <c r="K31" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="L31" s="11" t="s">
+        <v>71</v>
+      </c>
+      <c r="M31" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="N31" s="12" t="s">
+        <v>74</v>
+      </c>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A32" s="8"/>

--- a/12600512.xlsx
+++ b/12600512.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\vaults\my vault\01-academics\01-semester\02-cap776-python\04-assignments\daily-activity-tracker\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF247376-EC90-436C-AB7E-011D3E08C28D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC92CDB0-7850-4BAE-9404-C96A57E538A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="78">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -260,6 +260,15 @@
   </si>
   <si>
     <t>Excited about the hackathon but it didn't go well</t>
+  </si>
+  <si>
+    <t>Went to Jyoti chock</t>
+  </si>
+  <si>
+    <t>Mars Demo test</t>
+  </si>
+  <si>
+    <t>Python CA on Mars</t>
   </si>
 </sst>
 </file>
@@ -2154,8 +2163,12 @@
       <c r="C31" s="9">
         <v>0</v>
       </c>
-      <c r="D31" s="9"/>
-      <c r="E31" s="9"/>
+      <c r="D31" s="9">
+        <v>260</v>
+      </c>
+      <c r="E31" s="9">
+        <v>90</v>
+      </c>
       <c r="F31" s="9">
         <v>100</v>
       </c>
@@ -2167,11 +2180,11 @@
       </c>
       <c r="I31" s="10">
         <f t="shared" si="0"/>
-        <v>580</v>
+        <v>930</v>
       </c>
       <c r="J31" s="10">
         <f t="shared" si="1"/>
-        <v>860</v>
+        <v>510</v>
       </c>
       <c r="K31" s="11" t="s">
         <v>49</v>
@@ -2187,92 +2200,186 @@
       </c>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A32" s="8"/>
-      <c r="B32" s="9"/>
-      <c r="C32" s="9"/>
-      <c r="D32" s="9"/>
-      <c r="E32" s="9"/>
-      <c r="F32" s="9"/>
-      <c r="G32" s="9"/>
-      <c r="H32" s="9"/>
-      <c r="I32" s="10" t="str">
+      <c r="A32" s="8">
+        <v>46277</v>
+      </c>
+      <c r="B32" s="9">
+        <v>420</v>
+      </c>
+      <c r="C32" s="9">
+        <v>0</v>
+      </c>
+      <c r="D32" s="9">
+        <v>300</v>
+      </c>
+      <c r="E32" s="9">
+        <v>140</v>
+      </c>
+      <c r="F32" s="9">
+        <v>0</v>
+      </c>
+      <c r="G32" s="9">
+        <v>0</v>
+      </c>
+      <c r="H32" s="9">
+        <v>0</v>
+      </c>
+      <c r="I32" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J32" s="10" t="str">
+        <v>860</v>
+      </c>
+      <c r="J32" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K32" s="11"/>
-      <c r="L32" s="11"/>
-      <c r="M32" s="11"/>
+        <v>580</v>
+      </c>
+      <c r="K32" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="L32" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="M32" s="11" t="s">
+        <v>51</v>
+      </c>
       <c r="N32" s="12"/>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A33" s="8"/>
-      <c r="B33" s="9"/>
-      <c r="C33" s="9"/>
-      <c r="D33" s="9"/>
-      <c r="E33" s="9"/>
-      <c r="F33" s="9"/>
-      <c r="G33" s="9"/>
-      <c r="H33" s="9"/>
-      <c r="I33" s="10" t="str">
+      <c r="A33" s="8">
+        <v>46278</v>
+      </c>
+      <c r="B33" s="9">
+        <v>420</v>
+      </c>
+      <c r="C33" s="9">
+        <v>0</v>
+      </c>
+      <c r="D33" s="9">
+        <v>0</v>
+      </c>
+      <c r="E33" s="9">
+        <v>30</v>
+      </c>
+      <c r="F33" s="9">
+        <v>0</v>
+      </c>
+      <c r="G33" s="9">
+        <v>0</v>
+      </c>
+      <c r="H33" s="9">
+        <v>0</v>
+      </c>
+      <c r="I33" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J33" s="10" t="str">
+        <v>450</v>
+      </c>
+      <c r="J33" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K33" s="11"/>
-      <c r="L33" s="11"/>
-      <c r="M33" s="11"/>
-      <c r="N33" s="12"/>
+        <v>990</v>
+      </c>
+      <c r="K33" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="L33" s="11" t="s">
+        <v>68</v>
+      </c>
+      <c r="M33" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="N33" s="12" t="s">
+        <v>75</v>
+      </c>
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A34" s="8"/>
-      <c r="B34" s="9"/>
-      <c r="C34" s="9"/>
-      <c r="D34" s="9"/>
-      <c r="E34" s="9"/>
-      <c r="F34" s="9"/>
-      <c r="G34" s="9"/>
-      <c r="H34" s="9"/>
-      <c r="I34" s="10" t="str">
+      <c r="A34" s="8">
+        <v>46279</v>
+      </c>
+      <c r="B34" s="9">
+        <v>540</v>
+      </c>
+      <c r="C34" s="9">
+        <v>0</v>
+      </c>
+      <c r="D34" s="9">
+        <v>300</v>
+      </c>
+      <c r="E34" s="9">
+        <v>90</v>
+      </c>
+      <c r="F34" s="9">
+        <v>200</v>
+      </c>
+      <c r="G34" s="9">
+        <v>4</v>
+      </c>
+      <c r="H34" s="9">
+        <v>0</v>
+      </c>
+      <c r="I34" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J34" s="10" t="str">
+        <v>1130</v>
+      </c>
+      <c r="J34" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K34" s="11"/>
-      <c r="L34" s="11"/>
-      <c r="M34" s="11"/>
-      <c r="N34" s="12"/>
+        <v>310</v>
+      </c>
+      <c r="K34" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="L34" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="M34" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="N34" s="12" t="s">
+        <v>76</v>
+      </c>
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A35" s="8"/>
-      <c r="B35" s="9"/>
-      <c r="C35" s="9"/>
-      <c r="D35" s="9"/>
-      <c r="E35" s="9"/>
-      <c r="F35" s="9"/>
-      <c r="G35" s="9"/>
-      <c r="H35" s="9"/>
-      <c r="I35" s="10" t="str">
+      <c r="A35" s="8">
+        <v>46280</v>
+      </c>
+      <c r="B35" s="9">
+        <v>390</v>
+      </c>
+      <c r="C35" s="9">
+        <v>0</v>
+      </c>
+      <c r="D35" s="9">
+        <v>300</v>
+      </c>
+      <c r="E35" s="9">
+        <v>120</v>
+      </c>
+      <c r="F35" s="9">
+        <v>350</v>
+      </c>
+      <c r="G35" s="9">
+        <v>7</v>
+      </c>
+      <c r="H35" s="9">
+        <v>0</v>
+      </c>
+      <c r="I35" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J35" s="10" t="str">
+        <v>1160</v>
+      </c>
+      <c r="J35" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K35" s="11"/>
-      <c r="L35" s="11"/>
-      <c r="M35" s="11"/>
-      <c r="N35" s="12"/>
+        <v>280</v>
+      </c>
+      <c r="K35" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="L35" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="M35" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="N35" s="12" t="s">
+        <v>77</v>
+      </c>
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A36" s="8"/>

--- a/12600512.xlsx
+++ b/12600512.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\vaults\my vault\01-academics\01-semester\02-cap776-python\04-assignments\daily-activity-tracker\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC92CDB0-7850-4BAE-9404-C96A57E538A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F39CC583-1AFF-4EA9-A2EF-84214A5DC7A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="79">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -269,6 +269,9 @@
   </si>
   <si>
     <t>Python CA on Mars</t>
+  </si>
+  <si>
+    <t>solved my 11th leetcode problem</t>
   </si>
 </sst>
 </file>
@@ -2382,70 +2385,138 @@
       </c>
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A36" s="8"/>
-      <c r="B36" s="9"/>
-      <c r="C36" s="9"/>
-      <c r="D36" s="9"/>
-      <c r="E36" s="9"/>
-      <c r="F36" s="9"/>
-      <c r="G36" s="9"/>
-      <c r="H36" s="9"/>
-      <c r="I36" s="10" t="str">
+      <c r="A36" s="8">
+        <v>46281</v>
+      </c>
+      <c r="B36" s="9">
+        <v>360</v>
+      </c>
+      <c r="C36" s="9">
+        <v>0</v>
+      </c>
+      <c r="D36" s="9">
+        <v>120</v>
+      </c>
+      <c r="E36" s="9">
+        <v>180</v>
+      </c>
+      <c r="F36" s="9">
+        <v>350</v>
+      </c>
+      <c r="G36" s="9">
+        <v>7</v>
+      </c>
+      <c r="H36" s="9">
+        <v>0</v>
+      </c>
+      <c r="I36" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J36" s="10" t="str">
+        <v>1010</v>
+      </c>
+      <c r="J36" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K36" s="11"/>
-      <c r="L36" s="11"/>
-      <c r="M36" s="11"/>
+        <v>430</v>
+      </c>
+      <c r="K36" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="L36" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="M36" s="11" t="s">
+        <v>51</v>
+      </c>
       <c r="N36" s="12"/>
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A37" s="8"/>
-      <c r="B37" s="9"/>
-      <c r="C37" s="9"/>
-      <c r="D37" s="9"/>
-      <c r="E37" s="9"/>
-      <c r="F37" s="9"/>
-      <c r="G37" s="9"/>
-      <c r="H37" s="9"/>
-      <c r="I37" s="10" t="str">
+      <c r="A37" s="8">
+        <v>46282</v>
+      </c>
+      <c r="B37" s="9">
+        <v>420</v>
+      </c>
+      <c r="C37" s="9">
+        <v>0</v>
+      </c>
+      <c r="D37" s="9">
+        <v>180</v>
+      </c>
+      <c r="E37" s="9">
+        <v>200</v>
+      </c>
+      <c r="F37" s="9">
+        <v>200</v>
+      </c>
+      <c r="G37" s="9">
+        <v>4</v>
+      </c>
+      <c r="H37" s="9">
+        <v>0</v>
+      </c>
+      <c r="I37" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J37" s="10" t="str">
+        <v>1000</v>
+      </c>
+      <c r="J37" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K37" s="11"/>
-      <c r="L37" s="11"/>
-      <c r="M37" s="11"/>
+        <v>440</v>
+      </c>
+      <c r="K37" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="L37" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="M37" s="11" t="s">
+        <v>51</v>
+      </c>
       <c r="N37" s="12"/>
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A38" s="8"/>
-      <c r="B38" s="9"/>
-      <c r="C38" s="9"/>
-      <c r="D38" s="9"/>
-      <c r="E38" s="9"/>
-      <c r="F38" s="9"/>
-      <c r="G38" s="9"/>
-      <c r="H38" s="9"/>
-      <c r="I38" s="10" t="str">
+      <c r="A38" s="8">
+        <v>46283</v>
+      </c>
+      <c r="B38" s="9">
+        <v>390</v>
+      </c>
+      <c r="C38" s="9">
+        <v>0</v>
+      </c>
+      <c r="D38" s="9">
+        <v>160</v>
+      </c>
+      <c r="E38" s="9">
+        <v>120</v>
+      </c>
+      <c r="F38" s="9">
+        <v>250</v>
+      </c>
+      <c r="G38" s="9">
+        <v>5</v>
+      </c>
+      <c r="H38" s="9">
+        <v>0</v>
+      </c>
+      <c r="I38" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J38" s="10" t="str">
+        <v>920</v>
+      </c>
+      <c r="J38" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K38" s="11"/>
-      <c r="L38" s="11"/>
-      <c r="M38" s="11"/>
-      <c r="N38" s="12"/>
+        <v>520</v>
+      </c>
+      <c r="K38" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="L38" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="M38" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="N38" s="12" t="s">
+        <v>78</v>
+      </c>
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A39" s="8"/>

--- a/12600512.xlsx
+++ b/12600512.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\vaults\my vault\01-academics\01-semester\02-cap776-python\04-assignments\daily-activity-tracker\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F39CC583-1AFF-4EA9-A2EF-84214A5DC7A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B86E612-CFC8-409A-AAC6-A1D54270E7EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="79">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -2519,69 +2519,135 @@
       </c>
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A39" s="8"/>
-      <c r="B39" s="9"/>
-      <c r="C39" s="9"/>
-      <c r="D39" s="9"/>
-      <c r="E39" s="9"/>
-      <c r="F39" s="9"/>
-      <c r="G39" s="9"/>
-      <c r="H39" s="9"/>
-      <c r="I39" s="10" t="str">
+      <c r="A39" s="8">
+        <v>46284</v>
+      </c>
+      <c r="B39" s="9">
+        <v>420</v>
+      </c>
+      <c r="C39" s="9">
+        <v>0</v>
+      </c>
+      <c r="D39" s="9">
+        <v>180</v>
+      </c>
+      <c r="E39" s="9">
+        <v>60</v>
+      </c>
+      <c r="F39" s="9">
+        <v>0</v>
+      </c>
+      <c r="G39" s="9">
+        <v>0</v>
+      </c>
+      <c r="H39" s="9">
+        <v>0</v>
+      </c>
+      <c r="I39" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J39" s="10" t="str">
+        <v>660</v>
+      </c>
+      <c r="J39" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K39" s="11"/>
-      <c r="L39" s="11"/>
-      <c r="M39" s="11"/>
+        <v>780</v>
+      </c>
+      <c r="K39" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="L39" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="M39" s="11" t="s">
+        <v>51</v>
+      </c>
       <c r="N39" s="12"/>
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A40" s="8"/>
-      <c r="B40" s="9"/>
-      <c r="C40" s="9"/>
-      <c r="D40" s="9"/>
-      <c r="E40" s="9"/>
-      <c r="F40" s="9"/>
-      <c r="G40" s="9"/>
-      <c r="H40" s="9"/>
-      <c r="I40" s="10" t="str">
+      <c r="A40" s="8">
+        <v>46285</v>
+      </c>
+      <c r="B40" s="9">
+        <v>400</v>
+      </c>
+      <c r="C40" s="9">
+        <v>0</v>
+      </c>
+      <c r="D40" s="9">
+        <v>200</v>
+      </c>
+      <c r="E40" s="9">
+        <v>150</v>
+      </c>
+      <c r="F40" s="9">
+        <v>0</v>
+      </c>
+      <c r="G40" s="9">
+        <v>0</v>
+      </c>
+      <c r="H40" s="9">
+        <v>0</v>
+      </c>
+      <c r="I40" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J40" s="10" t="str">
+        <v>750</v>
+      </c>
+      <c r="J40" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K40" s="11"/>
-      <c r="L40" s="11"/>
-      <c r="M40" s="11"/>
+        <v>690</v>
+      </c>
+      <c r="K40" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="L40" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="M40" s="11" t="s">
+        <v>51</v>
+      </c>
       <c r="N40" s="12"/>
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A41" s="8"/>
-      <c r="B41" s="9"/>
-      <c r="C41" s="9"/>
-      <c r="D41" s="9"/>
-      <c r="E41" s="9"/>
-      <c r="F41" s="9"/>
-      <c r="G41" s="9"/>
-      <c r="H41" s="9"/>
-      <c r="I41" s="10" t="str">
+      <c r="A41" s="8">
+        <v>46286</v>
+      </c>
+      <c r="B41" s="9">
+        <v>390</v>
+      </c>
+      <c r="C41" s="9">
+        <v>0</v>
+      </c>
+      <c r="D41" s="9">
+        <v>260</v>
+      </c>
+      <c r="E41" s="9">
+        <v>120</v>
+      </c>
+      <c r="F41" s="9">
+        <v>200</v>
+      </c>
+      <c r="G41" s="9">
+        <v>4</v>
+      </c>
+      <c r="H41" s="9">
+        <v>0</v>
+      </c>
+      <c r="I41" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J41" s="10" t="str">
+        <v>970</v>
+      </c>
+      <c r="J41" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K41" s="11"/>
-      <c r="L41" s="11"/>
-      <c r="M41" s="11"/>
+        <v>470</v>
+      </c>
+      <c r="K41" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="L41" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="M41" s="11" t="s">
+        <v>51</v>
+      </c>
       <c r="N41" s="12"/>
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.3">
